--- a/database/event/5219/event_5219_evp_summary.xlsx
+++ b/database/event/5219/event_5219_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.6816</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E2" t="n">
         <v>6.4635</v>
@@ -514,10 +514,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5093</v>
+        <v>8.492699999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>8.9969</v>
+        <v>9.391299999999999</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>8.9969</v>
+        <v>9.391299999999999</v>
       </c>
       <c r="N2" t="n">
         <v>383</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0401</v>
+        <v>5.8396</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5059</v>
+        <v>2.4227</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0187</v>
+        <v>1.8826</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0401</v>
+        <v>5.8396</v>
       </c>
       <c r="F3" t="n">
-        <v>6.0401</v>
+        <v>5.8396</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.1678</v>
+        <v>6.8534</v>
       </c>
       <c r="I3" t="n">
         <v>7.5785</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1965</v>
+        <v>5.4667</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1559</v>
+        <v>2.268</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6779</v>
+        <v>1.734</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1965</v>
+        <v>5.4667</v>
       </c>
       <c r="F4" t="n">
-        <v>5.1965</v>
+        <v>5.4667</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.845</v>
+        <v>6.2687</v>
       </c>
       <c r="I4" t="n">
-        <v>6.0382</v>
+        <v>6.6475</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6.0382</v>
+        <v>6.6475</v>
       </c>
       <c r="N4" t="n">
         <v>318</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.562</v>
+        <v>4.833</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8927</v>
+        <v>2.0051</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4216</v>
+        <v>1.4816</v>
       </c>
       <c r="E5" t="n">
-        <v>4.562</v>
+        <v>4.833</v>
       </c>
       <c r="F5" t="n">
-        <v>4.562</v>
+        <v>4.833</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8502</v>
+        <v>5.275</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9872</v>
+        <v>5.5471</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9872</v>
+        <v>5.5471</v>
       </c>
       <c r="N5" t="n">
         <v>267</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4671</v>
+        <v>4.4006</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8533</v>
+        <v>1.8257</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3832</v>
+        <v>1.3093</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4671</v>
+        <v>4.4006</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4671</v>
+        <v>4.4006</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7013</v>
+        <v>4.5971</v>
       </c>
       <c r="I6" t="n">
         <v>4.8342</v>
@@ -722,461 +722,461 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3175</v>
+        <v>3.7179</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3764</v>
+        <v>1.5425</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9188</v>
+        <v>1.0373</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3175</v>
+        <v>3.7179</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3175</v>
+        <v>3.7179</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3175</v>
+        <v>3.7179</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5077</v>
+        <v>3.877</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>383</v>
+        <v>291</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5077</v>
+        <v>3.877</v>
       </c>
       <c r="N7" t="n">
-        <v>383</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2825</v>
+        <v>3.4598</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3618</v>
+        <v>1.4354</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.9345</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2825</v>
+        <v>3.4598</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2825</v>
+        <v>3.4598</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2825</v>
+        <v>3.4598</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3286</v>
+        <v>3.6079</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3286</v>
+        <v>3.6079</v>
       </c>
       <c r="N8" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2057</v>
+        <v>3.2459</v>
       </c>
       <c r="C9" t="n">
-        <v>1.33</v>
+        <v>1.3467</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8737</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2057</v>
+        <v>3.2459</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2057</v>
+        <v>3.2459</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2057</v>
+        <v>3.2459</v>
       </c>
       <c r="I9" t="n">
-        <v>3.281</v>
+        <v>3.3286</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>256</v>
+        <v>195</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.281</v>
+        <v>3.3286</v>
       </c>
       <c r="N9" t="n">
-        <v>256</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.066</v>
+        <v>3.172</v>
       </c>
       <c r="C10" t="n">
-        <v>1.272</v>
+        <v>1.316</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8172</v>
+        <v>0.8198</v>
       </c>
       <c r="E10" t="n">
-        <v>3.066</v>
+        <v>3.172</v>
       </c>
       <c r="F10" t="n">
-        <v>3.066</v>
+        <v>3.172</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.066</v>
+        <v>3.172</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1381</v>
+        <v>3.5077</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>291</v>
+        <v>383</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1381</v>
+        <v>3.5077</v>
       </c>
       <c r="N10" t="n">
-        <v>291</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0366</v>
+        <v>3.1464</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2598</v>
+        <v>1.3054</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8054</v>
+        <v>0.8096</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0366</v>
+        <v>3.1464</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0366</v>
+        <v>3.1464</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0366</v>
+        <v>3.1464</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1079</v>
+        <v>3.281</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>207</v>
+        <v>256</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1079</v>
+        <v>3.281</v>
       </c>
       <c r="N11" t="n">
-        <v>207</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7466</v>
+        <v>2.9804</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1395</v>
+        <v>1.2365</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6882</v>
+        <v>0.7435</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7466</v>
+        <v>2.9804</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7466</v>
+        <v>2.9804</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7466</v>
+        <v>2.9804</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8374</v>
+        <v>3.1079</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>318</v>
+        <v>207</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8374</v>
+        <v>3.1079</v>
       </c>
       <c r="N12" t="n">
-        <v>318</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6467</v>
+        <v>2.8912</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0981</v>
+        <v>1.1995</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6478</v>
+        <v>0.7079</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6467</v>
+        <v>2.8912</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6467</v>
+        <v>2.8912</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6467</v>
+        <v>2.8912</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6838</v>
+        <v>3.0659</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>152</v>
+        <v>318</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6838</v>
+        <v>3.0659</v>
       </c>
       <c r="N13" t="n">
-        <v>152</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Kyojin</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6157</v>
+        <v>2.8095</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0852</v>
+        <v>1.1656</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6353</v>
+        <v>0.6754</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6157</v>
+        <v>2.8095</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6157</v>
+        <v>2.8095</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6157</v>
+        <v>2.8095</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6772</v>
+        <v>2.9544</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6772</v>
+        <v>2.9544</v>
       </c>
       <c r="N14" t="n">
-        <v>207</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4495</v>
+        <v>2.6172</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0162</v>
+        <v>1.0858</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5682</v>
+        <v>0.5988</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4495</v>
+        <v>2.6172</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4495</v>
+        <v>2.6172</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4495</v>
+        <v>2.6172</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4724</v>
+        <v>2.6838</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4724</v>
+        <v>2.6838</v>
       </c>
       <c r="N15" t="n">
-        <v>121</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kyojin</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3969</v>
+        <v>2.4313</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9944</v>
+        <v>1.0087</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3969</v>
+        <v>2.4313</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3969</v>
+        <v>2.4313</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3969</v>
+        <v>2.4313</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4646</v>
+        <v>2.4724</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>267</v>
+        <v>121</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4646</v>
+        <v>2.4724</v>
       </c>
       <c r="N16" t="n">
-        <v>267</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2063</v>
+        <v>2.1817</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9153</v>
+        <v>0.9051</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4699</v>
+        <v>0.4253</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2063</v>
+        <v>2.1817</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2063</v>
+        <v>2.1817</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2063</v>
+        <v>2.1817</v>
       </c>
       <c r="I17" t="n">
         <v>2.2372</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1276</v>
+        <v>2.0751</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8827</v>
+        <v>0.8609</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4381</v>
+        <v>0.3828</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1276</v>
+        <v>2.0751</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1276</v>
+        <v>2.0751</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1276</v>
+        <v>2.0751</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2495</v>
+        <v>2.1639</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>383</v>
+        <v>291</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2495</v>
+        <v>2.1639</v>
       </c>
       <c r="N18" t="n">
-        <v>383</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1142</v>
+        <v>2.0343</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8771</v>
+        <v>0.844</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4327</v>
+        <v>0.3666</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1142</v>
+        <v>2.0343</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1142</v>
+        <v>2.0343</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1142</v>
+        <v>2.0343</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1639</v>
+        <v>2.2495</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>291</v>
+        <v>383</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1639</v>
+        <v>2.2495</v>
       </c>
       <c r="N19" t="n">
-        <v>291</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20">
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0154</v>
+        <v>1.978</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8361</v>
+        <v>0.8206</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3928</v>
+        <v>0.3441</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0154</v>
+        <v>1.978</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0154</v>
+        <v>1.978</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0154</v>
+        <v>1.978</v>
       </c>
       <c r="I20" t="n">
         <v>2.0627</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8509</v>
+        <v>1.893</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7679</v>
+        <v>0.7854</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3264</v>
+        <v>0.3103</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8509</v>
+        <v>1.893</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8509</v>
+        <v>1.893</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8509</v>
+        <v>1.893</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8769</v>
+        <v>1.9575</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>152</v>
+        <v>246</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8769</v>
+        <v>1.9575</v>
       </c>
       <c r="N21" t="n">
-        <v>152</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6051</v>
+        <v>1.8303</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6659</v>
+        <v>0.7594</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2271</v>
+        <v>0.2853</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6051</v>
+        <v>1.8303</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6051</v>
+        <v>1.8303</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6051</v>
+        <v>1.8303</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6352</v>
+        <v>1.8769</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>246</v>
+        <v>152</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6352</v>
+        <v>1.8769</v>
       </c>
       <c r="N22" t="n">
-        <v>246</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4914</v>
+        <v>1.4638</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6188</v>
+        <v>0.6073</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1811</v>
+        <v>0.1393</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4914</v>
+        <v>1.4638</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4914</v>
+        <v>1.4638</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4914</v>
+        <v>1.4638</v>
       </c>
       <c r="I23" t="n">
         <v>1.5264</v>
@@ -1504,277 +1504,277 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4744</v>
+        <v>1.4572</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6117</v>
+        <v>0.6046</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1743</v>
+        <v>0.1366</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4744</v>
+        <v>1.4572</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4744</v>
+        <v>1.4572</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4744</v>
+        <v>1.4572</v>
       </c>
       <c r="I24" t="n">
-        <v>1.502</v>
+        <v>1.5196</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>246</v>
+        <v>207</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.502</v>
+        <v>1.5196</v>
       </c>
       <c r="N24" t="n">
-        <v>246</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3734</v>
+        <v>1.4525</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5698</v>
+        <v>0.6026</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1335</v>
+        <v>0.1348</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3734</v>
+        <v>1.4525</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3734</v>
+        <v>1.4525</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3734</v>
+        <v>1.4525</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4187</v>
+        <v>1.502</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>318</v>
+        <v>246</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.4187</v>
+        <v>1.502</v>
       </c>
       <c r="N25" t="n">
-        <v>318</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3684</v>
+        <v>1.4239</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5677</v>
+        <v>0.5907</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1314</v>
+        <v>0.1234</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3684</v>
+        <v>1.4239</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3684</v>
+        <v>1.4239</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3684</v>
+        <v>1.4239</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3748</v>
+        <v>1.448</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3748</v>
+        <v>1.448</v>
       </c>
       <c r="N26" t="n">
-        <v>105</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3438</v>
+        <v>1.3633</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5575</v>
+        <v>0.5656</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1215</v>
+        <v>0.0992</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3438</v>
+        <v>1.3633</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3438</v>
+        <v>1.3633</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3438</v>
+        <v>1.3633</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3754</v>
+        <v>1.3748</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3754</v>
+        <v>1.3748</v>
       </c>
       <c r="N27" t="n">
-        <v>207</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3083</v>
+        <v>1.3379</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5551</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1072</v>
+        <v>0.0891</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3083</v>
+        <v>1.3379</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3083</v>
+        <v>1.3379</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3083</v>
+        <v>1.3379</v>
       </c>
       <c r="I28" t="n">
-        <v>1.339</v>
+        <v>1.4187</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>240</v>
+        <v>318</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.339</v>
+        <v>1.4187</v>
       </c>
       <c r="N28" t="n">
-        <v>240</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0855</v>
+        <v>1.2841</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4504</v>
+        <v>0.5327</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0172</v>
+        <v>0.0677</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0855</v>
+        <v>1.2841</v>
       </c>
       <c r="F29" t="n">
-        <v>1.0855</v>
+        <v>1.2841</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.0855</v>
+        <v>1.2841</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0855</v>
+        <v>1.339</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>68</v>
+        <v>240</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.0855</v>
+        <v>1.339</v>
       </c>
       <c r="N29" t="n">
-        <v>68</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0829</v>
+        <v>1.2737</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4493</v>
+        <v>0.5284</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0161</v>
+        <v>0.0635</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0829</v>
+        <v>1.2737</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0829</v>
+        <v>1.2737</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0829</v>
+        <v>1.2737</v>
       </c>
       <c r="I30" t="n">
-        <v>1.093</v>
+        <v>1.2952</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.093</v>
+        <v>1.2952</v>
       </c>
       <c r="N30" t="n">
         <v>178</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0419</v>
+        <v>1.11</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4323</v>
+        <v>0.4605</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0005</v>
+        <v>-0.0017</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0419</v>
+        <v>1.11</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0419</v>
+        <v>1.11</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0419</v>
+        <v>1.11</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0566</v>
+        <v>1.1383</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0566</v>
+        <v>1.1383</v>
       </c>
       <c r="N31" t="n">
         <v>195</v>
@@ -1872,170 +1872,170 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.0062</v>
+        <v>1.0855</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4175</v>
+        <v>0.4504</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0149</v>
+        <v>-0.0114</v>
       </c>
       <c r="E32" t="n">
-        <v>1.0062</v>
+        <v>1.0855</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0062</v>
+        <v>1.0855</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0062</v>
+        <v>1.0855</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0203</v>
+        <v>1.0855</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.0203</v>
+        <v>1.0855</v>
       </c>
       <c r="N32" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9922</v>
+        <v>0.995</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4116</v>
+        <v>0.4128</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0205</v>
+        <v>-0.0475</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9922</v>
+        <v>0.995</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9922</v>
+        <v>0.995</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9922</v>
+        <v>0.995</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9922</v>
+        <v>1.0203</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9922</v>
+        <v>1.0203</v>
       </c>
       <c r="N33" t="n">
-        <v>88</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>poizon</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8994</v>
+        <v>0.9922</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3731</v>
+        <v>0.4116</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.058</v>
+        <v>-0.0486</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8994</v>
+        <v>0.9922</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8994</v>
+        <v>0.9922</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8994</v>
+        <v>0.9922</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9205</v>
+        <v>0.9922</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>256</v>
+        <v>88</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9205</v>
+        <v>0.9922</v>
       </c>
       <c r="N34" t="n">
-        <v>256</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>poizon</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7905</v>
+        <v>0.8827</v>
       </c>
       <c r="C35" t="n">
-        <v>0.328</v>
+        <v>0.3662</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.102</v>
+        <v>-0.0922</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7905</v>
+        <v>0.8827</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7905</v>
+        <v>0.8827</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7905</v>
+        <v>0.8827</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8091</v>
+        <v>0.9205</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8091</v>
+        <v>0.9205</v>
       </c>
       <c r="N35" t="n">
         <v>256</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6335</v>
+        <v>0.7759</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2628</v>
+        <v>0.3219</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1654</v>
+        <v>-0.1348</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6335</v>
+        <v>0.7759</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6335</v>
+        <v>0.7759</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6335</v>
+        <v>0.7759</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6394</v>
+        <v>0.8091</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6394</v>
+        <v>0.8091</v>
       </c>
       <c r="N36" t="n">
-        <v>178</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37">
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6019</v>
+        <v>0.5974</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2497</v>
+        <v>0.2478</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1782</v>
+        <v>-0.2059</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6019</v>
+        <v>0.5974</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6019</v>
+        <v>0.5974</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6019</v>
+        <v>0.5974</v>
       </c>
       <c r="I37" t="n">
         <v>0.6075</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5569</v>
+        <v>0.5528</v>
       </c>
       <c r="C38" t="n">
-        <v>0.231</v>
+        <v>0.2293</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1964</v>
+        <v>-0.2237</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5569</v>
+        <v>0.5528</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5569</v>
+        <v>0.5528</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5569</v>
+        <v>0.5528</v>
       </c>
       <c r="I38" t="n">
         <v>0.5621</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5173</v>
+        <v>0.5039</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2146</v>
+        <v>0.2091</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2124</v>
+        <v>-0.2432</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5173</v>
+        <v>0.5039</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5173</v>
+        <v>0.5039</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5173</v>
+        <v>0.5039</v>
       </c>
       <c r="I39" t="n">
         <v>0.5344</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5016</v>
+        <v>0.496</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2081</v>
+        <v>0.2058</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2187</v>
+        <v>-0.2463</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5016</v>
+        <v>0.496</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5016</v>
+        <v>0.496</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5016</v>
+        <v>0.496</v>
       </c>
       <c r="I40" t="n">
         <v>0.5086000000000001</v>
@@ -2286,814 +2286,814 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4228</v>
+        <v>0.4758</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1754</v>
+        <v>0.1974</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2506</v>
+        <v>-0.2544</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4228</v>
+        <v>0.4758</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4228</v>
+        <v>0.4758</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4228</v>
+        <v>0.4758</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4327</v>
+        <v>0.4962</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>291</v>
+        <v>207</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4327</v>
+        <v>0.4962</v>
       </c>
       <c r="N41" t="n">
-        <v>291</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3657</v>
+        <v>0.415</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1517</v>
+        <v>0.1722</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2736</v>
+        <v>-0.2786</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3657</v>
+        <v>0.415</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3657</v>
+        <v>0.415</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3657</v>
+        <v>0.415</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3674</v>
+        <v>0.4327</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3674</v>
+        <v>0.4327</v>
       </c>
       <c r="N42" t="n">
-        <v>105</v>
+        <v>291</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>zehN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2565</v>
+        <v>0.408</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1064</v>
+        <v>0.1693</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3177</v>
+        <v>-0.2814</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2565</v>
+        <v>0.408</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2565</v>
+        <v>0.408</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2565</v>
+        <v>0.408</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2625</v>
+        <v>0.4184</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2625</v>
+        <v>0.4184</v>
       </c>
       <c r="N43" t="n">
-        <v>240</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2054</v>
+        <v>0.3643</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0852</v>
+        <v>0.1511</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3384</v>
+        <v>-0.2988</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2054</v>
+        <v>0.3643</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2054</v>
+        <v>0.3643</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2054</v>
+        <v>0.3643</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2112</v>
+        <v>0.3674</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>267</v>
+        <v>105</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2112</v>
+        <v>0.3674</v>
       </c>
       <c r="N44" t="n">
-        <v>267</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1882</v>
+        <v>0.2517</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0781</v>
+        <v>0.1044</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3453</v>
+        <v>-0.3436</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1882</v>
+        <v>0.2517</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1882</v>
+        <v>0.2517</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1882</v>
+        <v>0.2517</v>
       </c>
       <c r="I45" t="n">
-        <v>0.19</v>
+        <v>0.2625</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.19</v>
+        <v>0.2625</v>
       </c>
       <c r="N45" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jackinho</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0401</v>
+        <v>0.2008</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0166</v>
+        <v>0.0833</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4052</v>
+        <v>-0.3639</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0401</v>
+        <v>0.2008</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0401</v>
+        <v>0.2008</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0401</v>
+        <v>0.2008</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0403</v>
+        <v>0.2112</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0403</v>
+        <v>0.2112</v>
       </c>
       <c r="N46" t="n">
-        <v>105</v>
+        <v>267</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0436</v>
+        <v>0.1868</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0181</v>
+        <v>0.0775</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.439</v>
+        <v>-0.3695</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0436</v>
+        <v>0.1868</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0436</v>
+        <v>0.1868</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0436</v>
+        <v>0.1868</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0448</v>
+        <v>0.19</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>267</v>
+        <v>178</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0448</v>
+        <v>0.19</v>
       </c>
       <c r="N47" t="n">
-        <v>267</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Farlig</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0862</v>
+        <v>0.0998</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0358</v>
+        <v>0.0414</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4562</v>
+        <v>-0.4042</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0862</v>
+        <v>0.0998</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0862</v>
+        <v>0.0998</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0862</v>
+        <v>0.0998</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.1032</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>195</v>
+        <v>246</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.1032</v>
       </c>
       <c r="N48" t="n">
-        <v>195</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Jackinho</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1498</v>
+        <v>0.04</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0621</v>
+        <v>0.0166</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4819</v>
+        <v>-0.428</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1498</v>
+        <v>0.04</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1498</v>
+        <v>0.04</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1498</v>
+        <v>0.04</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1547</v>
+        <v>0.0403</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>318</v>
+        <v>105</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1547</v>
+        <v>0.0403</v>
       </c>
       <c r="N49" t="n">
-        <v>318</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1989</v>
+        <v>0.0172</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0825</v>
+        <v>0.0071</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5017</v>
+        <v>-0.4371</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1989</v>
+        <v>0.0172</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1989</v>
+        <v>0.0172</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1989</v>
+        <v>0.0172</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2036</v>
+        <v>0.0181</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.2036</v>
+        <v>0.0181</v>
       </c>
       <c r="N50" t="n">
-        <v>240</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Farlig</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2199</v>
+        <v>-0.0852</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0912</v>
+        <v>-0.0353</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5102</v>
+        <v>-0.4779</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.2199</v>
+        <v>-0.0852</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2199</v>
+        <v>-0.0852</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2199</v>
+        <v>-0.0852</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2251</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>256</v>
+        <v>195</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.2251</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>256</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3813</v>
+        <v>-0.1459</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1582</v>
+        <v>-0.0605</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5754</v>
+        <v>-0.502</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.3813</v>
+        <v>-0.1459</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3813</v>
+        <v>-0.1459</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.3813</v>
+        <v>-0.1459</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.3849</v>
+        <v>-0.1547</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>121</v>
+        <v>318</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.3849</v>
+        <v>-0.1547</v>
       </c>
       <c r="N52" t="n">
-        <v>121</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kressy</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3866</v>
+        <v>-0.1952</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1604</v>
+        <v>-0.081</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5775</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3866</v>
+        <v>-0.1952</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3866</v>
+        <v>-0.1952</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3866</v>
+        <v>-0.1952</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3866</v>
+        <v>-0.2036</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>88</v>
+        <v>240</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3866</v>
+        <v>-0.2036</v>
       </c>
       <c r="N53" t="n">
-        <v>88</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3881</v>
+        <v>-0.2159</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.161</v>
+        <v>-0.0896</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.5299</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3881</v>
+        <v>-0.2159</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3881</v>
+        <v>-0.2159</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3881</v>
+        <v>-0.2159</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3881</v>
+        <v>-0.2251</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>63</v>
+        <v>256</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3881</v>
+        <v>-0.2251</v>
       </c>
       <c r="N54" t="n">
-        <v>63</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4097</v>
+        <v>-0.3078</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.17</v>
+        <v>-0.1277</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5869</v>
+        <v>-0.5665</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4097</v>
+        <v>-0.3078</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4097</v>
+        <v>-0.3078</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4097</v>
+        <v>-0.3078</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4193</v>
+        <v>-0.313</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.4193</v>
+        <v>-0.313</v>
       </c>
       <c r="N55" t="n">
-        <v>207</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>zehN</t>
+          <t>kressy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4399</v>
+        <v>-0.3866</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1825</v>
+        <v>-0.1604</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5991</v>
+        <v>-0.5979</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4399</v>
+        <v>-0.3866</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4399</v>
+        <v>-0.3866</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4399</v>
+        <v>-0.3866</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.446</v>
+        <v>-0.3866</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>195</v>
+        <v>88</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.446</v>
+        <v>-0.3866</v>
       </c>
       <c r="N56" t="n">
-        <v>195</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FaNg</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.4579</v>
+        <v>-0.3881</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.19</v>
+        <v>-0.161</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6063</v>
+        <v>-0.5985</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4579</v>
+        <v>-0.3881</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.4579</v>
+        <v>-0.3881</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.4579</v>
+        <v>-0.3881</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.4579</v>
+        <v>-0.3881</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.4579</v>
+        <v>-0.3881</v>
       </c>
       <c r="N57" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>FaNg</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.4579</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2139</v>
+        <v>-0.19</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6297</v>
+        <v>-0.6263</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.4579</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.4579</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.4579</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.4579</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.4579</v>
       </c>
       <c r="N58" t="n">
         <v>68</v>
@@ -3114,93 +3114,93 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5327</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.221</v>
+        <v>-0.2139</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.6493</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5327</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5327</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5327</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5377</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5377</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="N59" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6086</v>
+        <v>-0.5288</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2525</v>
+        <v>-0.2194</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6672</v>
+        <v>-0.6546</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6086</v>
+        <v>-0.5288</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.6086</v>
+        <v>-0.5288</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.6086</v>
+        <v>-0.5288</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.62</v>
+        <v>-0.5377</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>246</v>
+        <v>121</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.62</v>
+        <v>-0.5377</v>
       </c>
       <c r="N60" t="n">
-        <v>246</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61">
@@ -3216,7 +3216,7 @@
         <v>-0.2608</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6753</v>
+        <v>-0.6943</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6286</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6613</v>
+        <v>-0.6589</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2744</v>
+        <v>-0.2734</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6885</v>
+        <v>-0.7064</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6613</v>
+        <v>-0.6589</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6613</v>
+        <v>-0.6589</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6613</v>
+        <v>-0.6589</v>
       </c>
       <c r="I62" t="n">
         <v>-0.6644</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2812</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.7139</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6777</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3327</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7453</v>
+        <v>-0.7634</v>
       </c>
       <c r="E64" t="n">
         <v>-0.8018999999999999</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3436</v>
+        <v>-0.3423</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7559</v>
+        <v>-0.7726</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="I65" t="n">
         <v>-0.832</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3715</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7831</v>
+        <v>-0.8007</v>
       </c>
       <c r="E66" t="n">
         <v>-0.8955</v>
@@ -3482,47 +3482,47 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>emi</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.0568</v>
+        <v>-0.9716</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4384</v>
+        <v>-0.4031</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.831</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.0568</v>
+        <v>-0.9716</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.0568</v>
+        <v>-0.9716</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.0568</v>
+        <v>-0.9716</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0568</v>
+        <v>-0.9963</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>88</v>
+        <v>195</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.0568</v>
+        <v>-0.9963</v>
       </c>
       <c r="N67" t="n">
-        <v>88</v>
+        <v>195</v>
       </c>
     </row>
     <row r="68">
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0645</v>
+        <v>-1.0565</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4416</v>
+        <v>-0.4383</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8514</v>
+        <v>-0.8648</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0645</v>
+        <v>-1.0565</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.0645</v>
+        <v>-1.0565</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.0645</v>
+        <v>-1.0565</v>
       </c>
       <c r="I68" t="n">
         <v>-1.0744</v>
@@ -3574,231 +3574,231 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>emi</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1654</v>
+        <v>-1.0568</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4835</v>
+        <v>-0.4384</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8922</v>
+        <v>-0.8649</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1654</v>
+        <v>-1.0568</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1654</v>
+        <v>-1.0568</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1654</v>
+        <v>-1.0568</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1817</v>
+        <v>-1.0568</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>195</v>
+        <v>88</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.1817</v>
+        <v>-1.0568</v>
       </c>
       <c r="N69" t="n">
-        <v>195</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.1664</v>
+        <v>-1.1629</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4839</v>
+        <v>-0.4825</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8925999999999999</v>
+        <v>-0.9072</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.1664</v>
+        <v>-1.1629</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.1664</v>
+        <v>-1.1629</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.1664</v>
+        <v>-1.1629</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1664</v>
+        <v>-1.2127</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>68</v>
+        <v>291</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.1664</v>
+        <v>-1.2127</v>
       </c>
       <c r="N70" t="n">
-        <v>68</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ckzao</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.2626</v>
+        <v>-1.1664</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5238</v>
+        <v>-0.4839</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9314</v>
+        <v>-0.9086</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2626</v>
+        <v>-1.1664</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.2626</v>
+        <v>-1.1664</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.2626</v>
+        <v>-1.1664</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2626</v>
+        <v>-1.1664</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.2626</v>
+        <v>-1.1664</v>
       </c>
       <c r="N71" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>ckzao</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.2888</v>
+        <v>-1.2626</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5347</v>
+        <v>-0.5238</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.9469</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.2888</v>
+        <v>-1.2626</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.2888</v>
+        <v>-1.2626</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.2888</v>
+        <v>-1.2626</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.3191</v>
+        <v>-1.2626</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>240</v>
+        <v>63</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.3191</v>
+        <v>-1.2626</v>
       </c>
       <c r="N72" t="n">
-        <v>240</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.3405</v>
+        <v>-1.265</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5561</v>
+        <v>-0.5248</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9629</v>
+        <v>-0.9479</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.3405</v>
+        <v>-1.265</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.3405</v>
+        <v>-1.265</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.3405</v>
+        <v>-1.265</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.372</v>
+        <v>-1.3191</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.372</v>
+        <v>-1.3191</v>
       </c>
       <c r="N73" t="n">
-        <v>291</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74">
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.3618</v>
+        <v>-1.3517</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5608</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9715</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.3618</v>
+        <v>-1.3517</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.3618</v>
+        <v>-1.3517</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.3618</v>
+        <v>-1.3517</v>
       </c>
       <c r="I74" t="n">
         <v>-1.3745</v>
@@ -3860,7 +3860,7 @@
         <v>-0.581</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9871</v>
+        <v>-1.0018</v>
       </c>
       <c r="E75" t="n">
         <v>-1.4004</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.7099</v>
+        <v>-1.6783</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7094</v>
+        <v>-0.6963</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1121</v>
+        <v>-1.1125</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.7099</v>
+        <v>-1.6783</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.7099</v>
+        <v>-1.6783</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.7099</v>
+        <v>-1.6783</v>
       </c>
       <c r="I76" t="n">
         <v>-1.7501</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7216</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.124</v>
+        <v>-1.1368</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7393</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.7716</v>
+        <v>-1.7453</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.735</v>
+        <v>-0.7241</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.137</v>
+        <v>-1.1392</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.7716</v>
+        <v>-1.7453</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.7716</v>
+        <v>-1.7453</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.7716</v>
+        <v>-1.7453</v>
       </c>
       <c r="I78" t="n">
         <v>-1.8048</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.98</v>
+        <v>-1.9433</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.8215</v>
+        <v>-0.8062</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2212</v>
+        <v>-1.2181</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.98</v>
+        <v>-1.9433</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.98</v>
+        <v>-1.9433</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.98</v>
+        <v>-1.9433</v>
       </c>
       <c r="I79" t="n">
         <v>-2.0265</v>
@@ -4080,93 +4080,93 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.3398</v>
+        <v>-1.9763</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.9707</v>
+        <v>-0.8199</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3666</v>
+        <v>-1.2313</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.3398</v>
+        <v>-1.9763</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.3398</v>
+        <v>-1.9763</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.3398</v>
+        <v>-1.9763</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.3837</v>
+        <v>-2.1854</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>246</v>
+        <v>383</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.3837</v>
+        <v>-2.1854</v>
       </c>
       <c r="N80" t="n">
-        <v>246</v>
+        <v>383</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.8816</v>
+        <v>-2.3051</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.1955</v>
+        <v>-0.9563</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5855</v>
+        <v>-1.3623</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.8816</v>
+        <v>-2.3051</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.8816</v>
+        <v>-2.3051</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.8816</v>
+        <v>-2.3051</v>
       </c>
       <c r="I81" t="n">
-        <v>-3.0468</v>
+        <v>-2.3837</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>383</v>
+        <v>246</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.0468</v>
+        <v>-2.3837</v>
       </c>
       <c r="N81" t="n">
-        <v>383</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
